--- a/education_forms/029_heron_s_formula_math_quiz--education_forms.xlsx
+++ b/education_forms/029_heron_s_formula_math_quiz--education_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,12 +510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_input</t>
+          <t>herons_formula</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is the length of side a</t>
+          <t>What is the formula for the area of a triangle?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,12 +533,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>user_input_2</t>
+          <t>side_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is the length of side b</t>
+          <t>What is the length of side a?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_input_3</t>
+          <t>side_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is the length of side c</t>
+          <t>What is the length of side b?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>user_input_4</t>
+          <t>side_c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is the length of side a</t>
+          <t>What is the length of side c?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_input_5</t>
+          <t>herons_result</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is the length of side b</t>
+          <t>What is the area of the triangle using Heron's formula?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_input_6</t>
+          <t>equal_sides_case</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the length of side c</t>
+          <t>How does Heron's formula handle the case where two sides are equal?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>side_length_effect</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the area of the triangle</t>
+          <t>What is the effect of increasing the length of one side on the area of the triangle?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,18 +671,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>result_2</t>
+          <t>example_triangle</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How many times did I get it wrong</t>
+          <t>Can you provide an example of a triangle with equal sides?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>min_required_sides</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>What is the minimum number of sides required to use Heron's formula?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
